--- a/data/legislation/coding/es_statements.xlsx
+++ b/data/legislation/coding/es_statements.xlsx
@@ -607,7 +607,7 @@
     <t>reviewed_no_change</t>
   </si>
   <si>
-    <t>reviewed_claude_pending_author</t>
+    <t>reviewed_changed</t>
   </si>
   <si>
     <t>Heading of a policy section, not a statement.</t>

--- a/data/legislation/coding/es_statements.xlsx
+++ b/data/legislation/coding/es_statements.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="211">
   <si>
     <t>document_id</t>
   </si>
@@ -127,9 +127,6 @@
     <t>auto_decision_authority</t>
   </si>
   <si>
-    <t>review_status</t>
-  </si>
-  <si>
     <t>review_notes</t>
   </si>
   <si>
@@ -602,12 +599,6 @@
   </si>
   <si>
     <t>non_central_only</t>
-  </si>
-  <si>
-    <t>reviewed_no_change</t>
-  </si>
-  <si>
-    <t>reviewed_changed</t>
   </si>
   <si>
     <t>Heading of a policy section, not a statement.</t>
@@ -987,10 +978,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AL72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:39">
+    <row r="1" spans="1:38">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1105,31 +1096,28 @@
       <c r="AL1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+    </row>
+    <row r="2" spans="1:38">
+      <c r="A2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="2" spans="1:39">
-      <c r="A2" t="s">
-        <v>39</v>
-      </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E2">
         <v>1999</v>
       </c>
       <c r="F2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H2">
         <v>24</v>
@@ -1138,7 +1126,7 @@
         <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -1153,10 +1141,10 @@
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
@@ -1201,51 +1189,48 @@
         <v>0</v>
       </c>
       <c r="AE2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AF2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG2">
         <v>0</v>
       </c>
       <c r="AH2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK2" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:39">
+    <row r="3" spans="1:38">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E3">
         <v>1999</v>
       </c>
       <c r="F3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H3">
         <v>196</v>
@@ -1254,7 +1239,7 @@
         <v>53</v>
       </c>
       <c r="J3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -1269,10 +1254,10 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
@@ -1317,51 +1302,48 @@
         <v>0</v>
       </c>
       <c r="AE3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG3">
         <v>0</v>
       </c>
       <c r="AH3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK3" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="4" spans="1:39">
+    <row r="4" spans="1:38">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E4">
         <v>1999</v>
       </c>
       <c r="F4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H4">
         <v>235</v>
@@ -1370,7 +1352,7 @@
         <v>9</v>
       </c>
       <c r="J4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -1385,10 +1367,10 @@
         <v>1</v>
       </c>
       <c r="O4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
@@ -1433,51 +1415,48 @@
         <v>0</v>
       </c>
       <c r="AE4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG4">
         <v>0</v>
       </c>
       <c r="AH4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI4" t="s">
         <v>11</v>
       </c>
       <c r="AJ4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK4" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="5" spans="1:39">
+    <row r="5" spans="1:38">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E5">
         <v>1999</v>
       </c>
       <c r="F5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H5">
         <v>273</v>
@@ -1486,7 +1465,7 @@
         <v>6</v>
       </c>
       <c r="J5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -1501,10 +1480,10 @@
         <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -1549,51 +1528,48 @@
         <v>0</v>
       </c>
       <c r="AE5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG5">
         <v>0</v>
       </c>
       <c r="AH5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI5" t="s">
         <v>11</v>
       </c>
       <c r="AJ5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK5" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="6" spans="1:39">
+    <row r="6" spans="1:38">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E6">
         <v>2001</v>
       </c>
       <c r="F6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H6">
         <v>17</v>
@@ -1602,7 +1578,7 @@
         <v>50</v>
       </c>
       <c r="J6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -1617,10 +1593,10 @@
         <v>1</v>
       </c>
       <c r="O6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
@@ -1665,51 +1641,48 @@
         <v>0</v>
       </c>
       <c r="AE6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AF6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG6">
         <v>0</v>
       </c>
       <c r="AH6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI6" t="s">
         <v>11</v>
       </c>
       <c r="AJ6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK6" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="7" spans="1:39">
+    <row r="7" spans="1:38">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E7">
         <v>2001</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H7">
         <v>23</v>
@@ -1718,7 +1691,7 @@
         <v>46</v>
       </c>
       <c r="J7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
@@ -1733,10 +1706,10 @@
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q7" t="b">
         <v>1</v>
@@ -1781,51 +1754,48 @@
         <v>0</v>
       </c>
       <c r="AE7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG7">
         <v>0</v>
       </c>
       <c r="AH7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI7" t="s">
         <v>11</v>
       </c>
       <c r="AJ7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK7" t="s">
-        <v>192</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:39">
+    <row r="8" spans="1:38">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E8">
         <v>2001</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H8">
         <v>27</v>
@@ -1834,7 +1804,7 @@
         <v>38</v>
       </c>
       <c r="J8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
@@ -1849,10 +1819,10 @@
         <v>1</v>
       </c>
       <c r="O8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q8" t="b">
         <v>1</v>
@@ -1897,51 +1867,48 @@
         <v>0</v>
       </c>
       <c r="AE8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG8">
         <v>0</v>
       </c>
       <c r="AH8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AI8" t="s">
         <v>12</v>
       </c>
       <c r="AJ8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK8" t="s">
-        <v>193</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
-    <row r="9" spans="1:39">
+    <row r="9" spans="1:38">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E9">
         <v>2001</v>
       </c>
       <c r="F9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H9">
         <v>143</v>
@@ -1950,7 +1917,7 @@
         <v>21</v>
       </c>
       <c r="J9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1965,10 +1932,10 @@
         <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q9" t="b">
         <v>0</v>
@@ -2013,51 +1980,48 @@
         <v>0</v>
       </c>
       <c r="AE9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG9">
         <v>0</v>
       </c>
       <c r="AH9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK9" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="10" spans="1:39">
+    <row r="10" spans="1:38">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E10">
         <v>2001</v>
       </c>
       <c r="F10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H10">
         <v>412</v>
@@ -2066,7 +2030,7 @@
         <v>36</v>
       </c>
       <c r="J10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -2081,10 +2045,10 @@
         <v>1</v>
       </c>
       <c r="O10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
@@ -2129,51 +2093,48 @@
         <v>0</v>
       </c>
       <c r="AE10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG10">
         <v>0</v>
       </c>
       <c r="AH10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK10" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="11" spans="1:39">
+    <row r="11" spans="1:38">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E11">
         <v>2001</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H11">
         <v>593</v>
@@ -2182,7 +2143,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
@@ -2197,10 +2158,10 @@
         <v>1</v>
       </c>
       <c r="O11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q11" t="b">
         <v>0</v>
@@ -2245,54 +2206,51 @@
         <v>0</v>
       </c>
       <c r="AE11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG11">
         <v>0</v>
       </c>
       <c r="AH11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL11" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
-    <row r="12" spans="1:39">
+    <row r="12" spans="1:38">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E12">
         <v>2001</v>
       </c>
       <c r="F12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H12">
         <v>595</v>
@@ -2301,7 +2259,7 @@
         <v>11</v>
       </c>
       <c r="J12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
@@ -2316,10 +2274,10 @@
         <v>1</v>
       </c>
       <c r="O12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
@@ -2364,51 +2322,48 @@
         <v>0</v>
       </c>
       <c r="AE12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG12">
         <v>0</v>
       </c>
       <c r="AH12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI12" t="s">
         <v>11</v>
       </c>
       <c r="AJ12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK12" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="13" spans="1:39">
+    <row r="13" spans="1:38">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E13">
         <v>2001</v>
       </c>
       <c r="F13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H13">
         <v>597</v>
@@ -2417,7 +2372,7 @@
         <v>28</v>
       </c>
       <c r="J13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
@@ -2432,10 +2387,10 @@
         <v>1</v>
       </c>
       <c r="O13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
@@ -2480,54 +2435,51 @@
         <v>0</v>
       </c>
       <c r="AE13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG13">
         <v>0</v>
       </c>
       <c r="AH13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI13" t="s">
         <v>11</v>
       </c>
       <c r="AJ13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL13" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
-    <row r="14" spans="1:39">
+    <row r="14" spans="1:38">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E14">
         <v>2001</v>
       </c>
       <c r="F14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H14">
         <v>915</v>
@@ -2536,7 +2488,7 @@
         <v>40</v>
       </c>
       <c r="J14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -2551,10 +2503,10 @@
         <v>1</v>
       </c>
       <c r="O14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
@@ -2599,51 +2551,48 @@
         <v>0</v>
       </c>
       <c r="AE14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG14">
         <v>0</v>
       </c>
       <c r="AH14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI14" t="s">
         <v>11</v>
       </c>
       <c r="AJ14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK14" t="s">
-        <v>192</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="15" spans="1:39">
+    <row r="15" spans="1:38">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E15">
         <v>2001</v>
       </c>
       <c r="F15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H15">
         <v>917</v>
@@ -2652,7 +2601,7 @@
         <v>20</v>
       </c>
       <c r="J15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2667,10 +2616,10 @@
         <v>1</v>
       </c>
       <c r="O15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
@@ -2715,54 +2664,51 @@
         <v>0</v>
       </c>
       <c r="AE15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG15">
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI15" t="s">
         <v>11</v>
       </c>
       <c r="AJ15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL15" t="s">
         <v>197</v>
       </c>
-      <c r="AM15" t="s">
-        <v>200</v>
-      </c>
     </row>
-    <row r="16" spans="1:39">
+    <row r="16" spans="1:38">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E16">
         <v>2007</v>
       </c>
       <c r="F16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H16">
         <v>33</v>
@@ -2771,7 +2717,7 @@
         <v>34</v>
       </c>
       <c r="J16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -2786,10 +2732,10 @@
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -2834,51 +2780,48 @@
         <v>0</v>
       </c>
       <c r="AE16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AF16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG16">
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK16" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL16" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="17" spans="1:39">
+    <row r="17" spans="1:38">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E17">
         <v>2007</v>
       </c>
       <c r="F17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H17">
         <v>119</v>
@@ -2887,7 +2830,7 @@
         <v>8</v>
       </c>
       <c r="J17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -2902,10 +2845,10 @@
         <v>1</v>
       </c>
       <c r="O17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q17" t="b">
         <v>0</v>
@@ -2950,51 +2893,48 @@
         <v>0</v>
       </c>
       <c r="AE17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG17">
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK17" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="18" spans="1:39">
+    <row r="18" spans="1:38">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E18">
         <v>2007</v>
       </c>
       <c r="F18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H18">
         <v>285</v>
@@ -3003,7 +2943,7 @@
         <v>51</v>
       </c>
       <c r="J18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
@@ -3018,10 +2958,10 @@
         <v>1</v>
       </c>
       <c r="O18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q18" t="b">
         <v>0</v>
@@ -3066,51 +3006,48 @@
         <v>0</v>
       </c>
       <c r="AE18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG18">
         <v>0</v>
       </c>
       <c r="AH18" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI18" t="s">
         <v>10</v>
       </c>
       <c r="AJ18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK18" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL18" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="19" spans="1:39">
+    <row r="19" spans="1:38">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E19">
         <v>2008</v>
       </c>
       <c r="F19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H19">
         <v>14</v>
@@ -3119,7 +3056,7 @@
         <v>50</v>
       </c>
       <c r="J19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
@@ -3134,10 +3071,10 @@
         <v>1</v>
       </c>
       <c r="O19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q19" t="b">
         <v>0</v>
@@ -3182,51 +3119,48 @@
         <v>0</v>
       </c>
       <c r="AE19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AF19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG19">
         <v>0</v>
       </c>
       <c r="AH19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI19" t="s">
         <v>11</v>
       </c>
       <c r="AJ19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK19" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL19" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="20" spans="1:39">
+    <row r="20" spans="1:38">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E20">
         <v>2008</v>
       </c>
       <c r="F20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H20">
         <v>20</v>
@@ -3235,7 +3169,7 @@
         <v>19</v>
       </c>
       <c r="J20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3250,10 +3184,10 @@
         <v>1</v>
       </c>
       <c r="O20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q20" t="b">
         <v>0</v>
@@ -3298,51 +3232,48 @@
         <v>0</v>
       </c>
       <c r="AE20" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AF20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG20">
         <v>0</v>
       </c>
       <c r="AH20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK20" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL20" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="21" spans="1:39">
+    <row r="21" spans="1:38">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E21">
         <v>2008</v>
       </c>
       <c r="F21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H21">
         <v>33</v>
@@ -3351,7 +3282,7 @@
         <v>8</v>
       </c>
       <c r="J21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -3366,10 +3297,10 @@
         <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q21" t="b">
         <v>0</v>
@@ -3414,51 +3345,48 @@
         <v>0</v>
       </c>
       <c r="AE21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG21">
         <v>0</v>
       </c>
       <c r="AH21" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI21" t="s">
         <v>11</v>
       </c>
       <c r="AJ21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK21" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL21" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="22" spans="1:39">
+    <row r="22" spans="1:38">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E22">
         <v>2008</v>
       </c>
       <c r="F22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H22">
         <v>43</v>
@@ -3467,7 +3395,7 @@
         <v>29</v>
       </c>
       <c r="J22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
@@ -3482,10 +3410,10 @@
         <v>1</v>
       </c>
       <c r="O22" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q22" t="b">
         <v>0</v>
@@ -3530,51 +3458,48 @@
         <v>0</v>
       </c>
       <c r="AE22" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG22">
         <v>0</v>
       </c>
       <c r="AH22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI22" t="s">
         <v>10</v>
       </c>
       <c r="AJ22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK22" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL22" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="23" spans="1:39">
+    <row r="23" spans="1:38">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E23">
         <v>2008</v>
       </c>
       <c r="F23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H23">
         <v>77</v>
@@ -3583,7 +3508,7 @@
         <v>7</v>
       </c>
       <c r="J23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
@@ -3598,10 +3523,10 @@
         <v>1</v>
       </c>
       <c r="O23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q23" t="b">
         <v>0</v>
@@ -3646,51 +3571,48 @@
         <v>0</v>
       </c>
       <c r="AE23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF23" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG23">
         <v>0</v>
       </c>
       <c r="AH23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI23" t="s">
         <v>11</v>
       </c>
       <c r="AJ23" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK23" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL23" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="24" spans="1:39">
+    <row r="24" spans="1:38">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E24">
         <v>2008</v>
       </c>
       <c r="F24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H24">
         <v>78</v>
@@ -3699,7 +3621,7 @@
         <v>47</v>
       </c>
       <c r="J24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -3714,10 +3636,10 @@
         <v>1</v>
       </c>
       <c r="O24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q24" t="b">
         <v>0</v>
@@ -3762,54 +3684,51 @@
         <v>0</v>
       </c>
       <c r="AE24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG24">
         <v>0</v>
       </c>
       <c r="AH24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI24" t="s">
         <v>11</v>
       </c>
       <c r="AJ24" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK24" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL24" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM24" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
-    <row r="25" spans="1:39">
+    <row r="25" spans="1:38">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E25">
         <v>2008</v>
       </c>
       <c r="F25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H25">
         <v>81</v>
@@ -3818,7 +3737,7 @@
         <v>29</v>
       </c>
       <c r="J25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -3833,10 +3752,10 @@
         <v>1</v>
       </c>
       <c r="O25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q25" t="b">
         <v>1</v>
@@ -3881,51 +3800,48 @@
         <v>0</v>
       </c>
       <c r="AE25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AF25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG25">
         <v>0</v>
       </c>
       <c r="AH25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI25" t="s">
         <v>11</v>
       </c>
       <c r="AJ25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AK25" t="s">
-        <v>192</v>
-      </c>
-      <c r="AL25" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="26" spans="1:39">
+    <row r="26" spans="1:38">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E26">
         <v>2008</v>
       </c>
       <c r="F26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H26">
         <v>82</v>
@@ -3934,7 +3850,7 @@
         <v>22</v>
       </c>
       <c r="J26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
@@ -3949,10 +3865,10 @@
         <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q26" t="b">
         <v>0</v>
@@ -3997,54 +3913,51 @@
         <v>0</v>
       </c>
       <c r="AE26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG26">
         <v>0</v>
       </c>
       <c r="AH26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI26" t="s">
         <v>11</v>
       </c>
       <c r="AJ26" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL26" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM26" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
-    <row r="27" spans="1:39">
+    <row r="27" spans="1:38">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E27">
         <v>2008</v>
       </c>
       <c r="F27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H27">
         <v>83</v>
@@ -4053,7 +3966,7 @@
         <v>14</v>
       </c>
       <c r="J27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -4068,10 +3981,10 @@
         <v>1</v>
       </c>
       <c r="O27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P27" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q27" t="b">
         <v>0</v>
@@ -4116,54 +4029,51 @@
         <v>0</v>
       </c>
       <c r="AE27" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG27">
         <v>0</v>
       </c>
       <c r="AH27" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI27" t="s">
         <v>11</v>
       </c>
       <c r="AJ27" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK27" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL27" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM27" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
-    <row r="28" spans="1:39">
+    <row r="28" spans="1:38">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E28">
         <v>2008</v>
       </c>
       <c r="F28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H28">
         <v>85</v>
@@ -4172,7 +4082,7 @@
         <v>15</v>
       </c>
       <c r="J28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
@@ -4187,10 +4097,10 @@
         <v>1</v>
       </c>
       <c r="O28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P28" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q28" t="b">
         <v>0</v>
@@ -4235,54 +4145,51 @@
         <v>0</v>
       </c>
       <c r="AE28" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF28" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG28">
         <v>0</v>
       </c>
       <c r="AH28" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI28" t="s">
         <v>11</v>
       </c>
       <c r="AJ28" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK28" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL28" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM28" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
-    <row r="29" spans="1:39">
+    <row r="29" spans="1:38">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E29">
         <v>2003</v>
       </c>
       <c r="F29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H29">
         <v>188</v>
@@ -4291,7 +4198,7 @@
         <v>12</v>
       </c>
       <c r="J29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -4306,10 +4213,10 @@
         <v>1</v>
       </c>
       <c r="O29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P29" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q29" t="b">
         <v>0</v>
@@ -4354,51 +4261,48 @@
         <v>0</v>
       </c>
       <c r="AE29" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG29">
         <v>0</v>
       </c>
       <c r="AH29" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI29" t="s">
         <v>11</v>
       </c>
       <c r="AJ29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK29" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL29" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="30" spans="1:39">
+    <row r="30" spans="1:38">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E30">
         <v>2003</v>
       </c>
       <c r="F30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H30">
         <v>40</v>
@@ -4407,7 +4311,7 @@
         <v>52</v>
       </c>
       <c r="J30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -4422,10 +4326,10 @@
         <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P30" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q30" t="b">
         <v>0</v>
@@ -4470,51 +4374,48 @@
         <v>0</v>
       </c>
       <c r="AE30" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AF30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG30">
         <v>0</v>
       </c>
       <c r="AH30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI30" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK30" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL30" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="31" spans="1:39">
+    <row r="31" spans="1:38">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E31">
         <v>2003</v>
       </c>
       <c r="F31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H31">
         <v>255</v>
@@ -4523,7 +4424,7 @@
         <v>56</v>
       </c>
       <c r="J31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -4538,10 +4439,10 @@
         <v>1</v>
       </c>
       <c r="O31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P31" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q31" t="b">
         <v>1</v>
@@ -4586,51 +4487,48 @@
         <v>1</v>
       </c>
       <c r="AE31" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AF31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG31">
         <v>1</v>
       </c>
       <c r="AH31" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI31" t="s">
         <v>11</v>
       </c>
       <c r="AJ31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AK31" t="s">
-        <v>192</v>
-      </c>
-      <c r="AL31" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="32" spans="1:39">
+    <row r="32" spans="1:38">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E32">
         <v>2008</v>
       </c>
       <c r="F32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H32">
         <v>98</v>
@@ -4639,7 +4537,7 @@
         <v>37</v>
       </c>
       <c r="J32" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -4654,10 +4552,10 @@
         <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q32" t="b">
         <v>1</v>
@@ -4702,51 +4600,48 @@
         <v>0</v>
       </c>
       <c r="AE32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF32" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG32">
         <v>0</v>
       </c>
       <c r="AH32" t="s">
+        <v>192</v>
+      </c>
+      <c r="AI32" t="s">
         <v>193</v>
       </c>
-      <c r="AI32" t="s">
-        <v>194</v>
-      </c>
       <c r="AJ32" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK32" t="s">
-        <v>193</v>
-      </c>
-      <c r="AL32" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
-    <row r="33" spans="1:39">
+    <row r="33" spans="1:38">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E33">
         <v>2008</v>
       </c>
       <c r="F33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H33">
         <v>104</v>
@@ -4755,7 +4650,7 @@
         <v>92</v>
       </c>
       <c r="J33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -4770,10 +4665,10 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P33" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q33" t="b">
         <v>0</v>
@@ -4818,54 +4713,51 @@
         <v>0</v>
       </c>
       <c r="AE33" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF33" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG33">
         <v>0</v>
       </c>
       <c r="AH33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI33" t="s">
         <v>11</v>
       </c>
       <c r="AJ33" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AL33" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
-    <row r="34" spans="1:39">
+    <row r="34" spans="1:38">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E34">
         <v>2008</v>
       </c>
       <c r="F34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H34">
         <v>125</v>
@@ -4874,7 +4766,7 @@
         <v>33</v>
       </c>
       <c r="J34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -4889,10 +4781,10 @@
         <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P34" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q34" t="b">
         <v>0</v>
@@ -4937,51 +4829,48 @@
         <v>0</v>
       </c>
       <c r="AE34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF34" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG34">
         <v>0</v>
       </c>
       <c r="AH34" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI34" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ34" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK34" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL34" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="35" spans="1:39">
+    <row r="35" spans="1:38">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E35">
         <v>2008</v>
       </c>
       <c r="F35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H35">
         <v>130</v>
@@ -4990,7 +4879,7 @@
         <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -5005,10 +4894,10 @@
         <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P35" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q35" t="b">
         <v>0</v>
@@ -5053,54 +4942,51 @@
         <v>0</v>
       </c>
       <c r="AE35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG35">
         <v>0</v>
       </c>
       <c r="AH35" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI35" t="s">
         <v>11</v>
       </c>
       <c r="AJ35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK35" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL35" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM35" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
-    <row r="36" spans="1:39">
+    <row r="36" spans="1:38">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E36">
         <v>2008</v>
       </c>
       <c r="F36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H36">
         <v>136</v>
@@ -5109,7 +4995,7 @@
         <v>65</v>
       </c>
       <c r="J36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -5124,10 +5010,10 @@
         <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P36" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q36" t="b">
         <v>0</v>
@@ -5172,51 +5058,48 @@
         <v>0</v>
       </c>
       <c r="AE36" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF36" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG36">
         <v>0</v>
       </c>
       <c r="AH36" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI36" t="s">
         <v>11</v>
       </c>
       <c r="AJ36" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK36" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL36" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="37" spans="1:39">
+    <row r="37" spans="1:38">
       <c r="A37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E37">
         <v>2008</v>
       </c>
       <c r="F37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H37">
         <v>137</v>
@@ -5225,7 +5108,7 @@
         <v>41</v>
       </c>
       <c r="J37" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
@@ -5240,10 +5123,10 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P37" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q37" t="b">
         <v>1</v>
@@ -5288,54 +5171,51 @@
         <v>0</v>
       </c>
       <c r="AE37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF37" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG37">
         <v>0</v>
       </c>
       <c r="AH37" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI37" t="s">
         <v>11</v>
       </c>
       <c r="AJ37" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK37" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AL37" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM37" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
-    <row r="38" spans="1:39">
+    <row r="38" spans="1:38">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E38">
         <v>2008</v>
       </c>
       <c r="F38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H38">
         <v>143</v>
@@ -5344,7 +5224,7 @@
         <v>58</v>
       </c>
       <c r="J38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -5359,10 +5239,10 @@
         <v>1</v>
       </c>
       <c r="O38" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P38" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q38" t="b">
         <v>0</v>
@@ -5407,51 +5287,48 @@
         <v>0</v>
       </c>
       <c r="AE38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AF38" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG38">
         <v>0</v>
       </c>
       <c r="AH38" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI38" t="s">
         <v>11</v>
       </c>
       <c r="AJ38" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK38" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL38" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="39" spans="1:39">
+    <row r="39" spans="1:38">
       <c r="A39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D39" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E39">
         <v>2008</v>
       </c>
       <c r="F39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H39">
         <v>147</v>
@@ -5460,7 +5337,7 @@
         <v>62</v>
       </c>
       <c r="J39" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
@@ -5475,10 +5352,10 @@
         <v>1</v>
       </c>
       <c r="O39" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P39" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q39" t="b">
         <v>1</v>
@@ -5523,51 +5400,48 @@
         <v>0</v>
       </c>
       <c r="AE39" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF39" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG39">
         <v>1</v>
       </c>
       <c r="AH39" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI39" t="s">
         <v>11</v>
       </c>
       <c r="AJ39" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK39" t="s">
-        <v>192</v>
-      </c>
-      <c r="AL39" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="40" spans="1:39">
+    <row r="40" spans="1:38">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E40">
         <v>2008</v>
       </c>
       <c r="F40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H40">
         <v>150</v>
@@ -5576,7 +5450,7 @@
         <v>49</v>
       </c>
       <c r="J40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -5591,10 +5465,10 @@
         <v>1</v>
       </c>
       <c r="O40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P40" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q40" t="b">
         <v>0</v>
@@ -5639,51 +5513,48 @@
         <v>0</v>
       </c>
       <c r="AE40" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AF40" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG40">
         <v>0</v>
       </c>
       <c r="AH40" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI40" t="s">
         <v>11</v>
       </c>
       <c r="AJ40" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK40" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL40" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:39">
+    <row r="41" spans="1:38">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E41">
         <v>2008</v>
       </c>
       <c r="F41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H41">
         <v>152</v>
@@ -5692,7 +5563,7 @@
         <v>40</v>
       </c>
       <c r="J41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -5707,10 +5578,10 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P41" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q41" t="b">
         <v>0</v>
@@ -5755,51 +5626,48 @@
         <v>0</v>
       </c>
       <c r="AE41" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF41" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG41">
         <v>0</v>
       </c>
       <c r="AH41" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI41" t="s">
         <v>11</v>
       </c>
       <c r="AJ41" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK41" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL41" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="42" spans="1:39">
+    <row r="42" spans="1:38">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E42">
         <v>2007</v>
       </c>
       <c r="F42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H42">
         <v>61</v>
@@ -5808,7 +5676,7 @@
         <v>77</v>
       </c>
       <c r="J42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -5823,10 +5691,10 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P42" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q42" t="b">
         <v>0</v>
@@ -5871,51 +5739,48 @@
         <v>0</v>
       </c>
       <c r="AE42" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AF42" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG42">
         <v>0</v>
       </c>
       <c r="AH42" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI42" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ42" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK42" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL42" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="43" spans="1:39">
+    <row r="43" spans="1:38">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D43" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E43">
         <v>2007</v>
       </c>
       <c r="F43" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H43">
         <v>107</v>
@@ -5924,7 +5789,7 @@
         <v>9</v>
       </c>
       <c r="J43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -5939,10 +5804,10 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P43" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q43" t="b">
         <v>0</v>
@@ -5987,51 +5852,48 @@
         <v>0</v>
       </c>
       <c r="AE43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF43" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG43">
         <v>0</v>
       </c>
       <c r="AH43" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI43" t="s">
         <v>11</v>
       </c>
       <c r="AJ43" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK43" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL43" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="44" spans="1:39">
+    <row r="44" spans="1:38">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E44">
         <v>2007</v>
       </c>
       <c r="F44" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H44">
         <v>108</v>
@@ -6040,7 +5902,7 @@
         <v>34</v>
       </c>
       <c r="J44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6055,10 +5917,10 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P44" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q44" t="b">
         <v>0</v>
@@ -6103,54 +5965,51 @@
         <v>0</v>
       </c>
       <c r="AE44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF44" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG44">
         <v>0</v>
       </c>
       <c r="AH44" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI44" t="s">
         <v>11</v>
       </c>
       <c r="AJ44" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK44" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL44" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM44" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
-    <row r="45" spans="1:39">
+    <row r="45" spans="1:38">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D45" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E45">
         <v>2007</v>
       </c>
       <c r="F45" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G45" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H45">
         <v>172</v>
@@ -6159,7 +6018,7 @@
         <v>45</v>
       </c>
       <c r="J45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6174,10 +6033,10 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P45" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q45" t="b">
         <v>0</v>
@@ -6222,54 +6081,51 @@
         <v>0</v>
       </c>
       <c r="AE45" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF45" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG45">
         <v>1</v>
       </c>
       <c r="AH45" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI45" t="s">
         <v>11</v>
       </c>
       <c r="AJ45" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK45" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL45" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM45" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
-    <row r="46" spans="1:39">
+    <row r="46" spans="1:38">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E46">
         <v>2007</v>
       </c>
       <c r="F46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G46" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H46">
         <v>400</v>
@@ -6278,7 +6134,7 @@
         <v>7</v>
       </c>
       <c r="J46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -6293,10 +6149,10 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P46" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q46" t="b">
         <v>0</v>
@@ -6341,51 +6197,48 @@
         <v>0</v>
       </c>
       <c r="AE46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG46">
         <v>0</v>
       </c>
       <c r="AH46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI46" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK46" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL46" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="47" spans="1:39">
+    <row r="47" spans="1:38">
       <c r="A47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E47">
         <v>2007</v>
       </c>
       <c r="F47" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H47">
         <v>401</v>
@@ -6394,7 +6247,7 @@
         <v>67</v>
       </c>
       <c r="J47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -6409,10 +6262,10 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P47" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q47" t="b">
         <v>0</v>
@@ -6457,51 +6310,48 @@
         <v>0</v>
       </c>
       <c r="AE47" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AF47" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG47">
         <v>0</v>
       </c>
       <c r="AH47" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI47" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ47" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK47" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL47" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="48" spans="1:39">
+    <row r="48" spans="1:38">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D48" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E48">
         <v>2007</v>
       </c>
       <c r="F48" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H48">
         <v>402</v>
@@ -6510,7 +6360,7 @@
         <v>32</v>
       </c>
       <c r="J48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -6525,10 +6375,10 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P48" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q48" t="b">
         <v>0</v>
@@ -6573,54 +6423,51 @@
         <v>0</v>
       </c>
       <c r="AE48" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AF48" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG48">
         <v>0</v>
       </c>
       <c r="AH48" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI48" t="s">
         <v>11</v>
       </c>
       <c r="AJ48" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK48" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL48" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM48" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
-    <row r="49" spans="1:39">
+    <row r="49" spans="1:38">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D49" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E49">
         <v>2007</v>
       </c>
       <c r="F49" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H49">
         <v>411</v>
@@ -6629,7 +6476,7 @@
         <v>36</v>
       </c>
       <c r="J49" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -6644,10 +6491,10 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P49" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q49" t="b">
         <v>0</v>
@@ -6692,51 +6539,48 @@
         <v>0</v>
       </c>
       <c r="AE49" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF49" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG49">
         <v>0</v>
       </c>
       <c r="AH49" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI49" t="s">
         <v>11</v>
       </c>
       <c r="AJ49" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AK49" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL49" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="50" spans="1:39">
+    <row r="50" spans="1:38">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E50">
         <v>2007</v>
       </c>
       <c r="F50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H50">
         <v>412</v>
@@ -6745,7 +6589,7 @@
         <v>24</v>
       </c>
       <c r="J50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -6760,10 +6604,10 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P50" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q50" t="b">
         <v>1</v>
@@ -6808,54 +6652,51 @@
         <v>0</v>
       </c>
       <c r="AE50" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG50">
         <v>0</v>
       </c>
       <c r="AH50" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI50" t="s">
         <v>11</v>
       </c>
       <c r="AJ50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK50" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AL50" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM50" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
-    <row r="51" spans="1:39">
+    <row r="51" spans="1:38">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C51" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E51">
         <v>2007</v>
       </c>
       <c r="F51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H51">
         <v>109</v>
@@ -6864,7 +6705,7 @@
         <v>17</v>
       </c>
       <c r="J51" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -6879,10 +6720,10 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P51" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q51" t="b">
         <v>0</v>
@@ -6927,54 +6768,51 @@
         <v>0</v>
       </c>
       <c r="AE51" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF51" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG51">
         <v>0</v>
       </c>
       <c r="AH51" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI51" t="s">
         <v>11</v>
       </c>
       <c r="AJ51" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AK51" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL51" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM51" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
-    <row r="52" spans="1:39">
+    <row r="52" spans="1:38">
       <c r="A52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C52" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D52" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E52">
         <v>2010</v>
       </c>
       <c r="F52" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H52">
         <v>96</v>
@@ -6983,7 +6821,7 @@
         <v>41</v>
       </c>
       <c r="J52" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K52" t="b">
         <v>0</v>
@@ -6998,10 +6836,10 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q52" t="b">
         <v>0</v>
@@ -7046,54 +6884,51 @@
         <v>0</v>
       </c>
       <c r="AE52" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AF52" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG52">
         <v>0</v>
       </c>
       <c r="AH52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI52" t="s">
         <v>11</v>
       </c>
       <c r="AJ52" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AK52" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL52" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM52" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
-    <row r="53" spans="1:39">
+    <row r="53" spans="1:38">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B53" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C53" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D53" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E53">
         <v>2020</v>
       </c>
       <c r="F53" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H53">
         <v>73</v>
@@ -7102,7 +6937,7 @@
         <v>77</v>
       </c>
       <c r="J53" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K53" t="b">
         <v>0</v>
@@ -7117,99 +6952,96 @@
         <v>1</v>
       </c>
       <c r="O53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P53" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q53" t="b">
+        <v>0</v>
+      </c>
+      <c r="R53" t="b">
+        <v>0</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="b">
+        <v>0</v>
+      </c>
+      <c r="U53" t="b">
+        <v>0</v>
+      </c>
+      <c r="V53" t="b">
+        <v>0</v>
+      </c>
+      <c r="W53" t="b">
+        <v>0</v>
+      </c>
+      <c r="X53" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="s">
         <v>184</v>
       </c>
-      <c r="Q53" t="b">
-        <v>0</v>
-      </c>
-      <c r="R53" t="b">
-        <v>0</v>
-      </c>
-      <c r="S53" t="b">
-        <v>0</v>
-      </c>
-      <c r="T53" t="b">
-        <v>0</v>
-      </c>
-      <c r="U53" t="b">
-        <v>0</v>
-      </c>
-      <c r="V53" t="b">
-        <v>0</v>
-      </c>
-      <c r="W53" t="b">
-        <v>0</v>
-      </c>
-      <c r="X53" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="s">
-        <v>185</v>
-      </c>
       <c r="AF53" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG53">
         <v>0</v>
       </c>
       <c r="AH53" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI53" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ53" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK53" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL53" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="54" spans="1:39">
+    <row r="54" spans="1:38">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C54" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D54" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E54">
         <v>2020</v>
       </c>
       <c r="F54" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G54" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H54">
         <v>112</v>
@@ -7218,7 +7050,7 @@
         <v>43</v>
       </c>
       <c r="J54" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K54" t="b">
         <v>0</v>
@@ -7233,10 +7065,10 @@
         <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P54" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q54" t="b">
         <v>0</v>
@@ -7281,51 +7113,48 @@
         <v>0</v>
       </c>
       <c r="AE54" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF54" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG54">
         <v>0</v>
       </c>
       <c r="AH54" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI54" t="s">
         <v>11</v>
       </c>
       <c r="AJ54" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK54" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL54" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="55" spans="1:39">
+    <row r="55" spans="1:38">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D55" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E55">
         <v>2020</v>
       </c>
       <c r="F55" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G55" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H55">
         <v>149</v>
@@ -7334,7 +7163,7 @@
         <v>42</v>
       </c>
       <c r="J55" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K55" t="b">
         <v>0</v>
@@ -7349,10 +7178,10 @@
         <v>1</v>
       </c>
       <c r="O55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P55" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q55" t="b">
         <v>0</v>
@@ -7397,54 +7226,51 @@
         <v>0</v>
       </c>
       <c r="AE55" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF55" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG55">
         <v>1</v>
       </c>
       <c r="AH55" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI55" t="s">
         <v>11</v>
       </c>
       <c r="AJ55" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AL55" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM55" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
-    <row r="56" spans="1:39">
+    <row r="56" spans="1:38">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B56" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C56" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D56" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E56">
         <v>2020</v>
       </c>
       <c r="F56" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G56" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H56">
         <v>183</v>
@@ -7453,7 +7279,7 @@
         <v>52</v>
       </c>
       <c r="J56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K56" t="b">
         <v>0</v>
@@ -7468,10 +7294,10 @@
         <v>1</v>
       </c>
       <c r="O56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P56" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q56" t="b">
         <v>1</v>
@@ -7516,51 +7342,48 @@
         <v>0</v>
       </c>
       <c r="AE56" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AF56" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG56">
         <v>0</v>
       </c>
       <c r="AH56" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI56" t="s">
         <v>11</v>
       </c>
       <c r="AJ56" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AK56" t="s">
-        <v>192</v>
-      </c>
-      <c r="AL56" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="57" spans="1:39">
+    <row r="57" spans="1:38">
       <c r="A57" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B57" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C57" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E57">
         <v>2020</v>
       </c>
       <c r="F57" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G57" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H57">
         <v>184</v>
@@ -7569,7 +7392,7 @@
         <v>44</v>
       </c>
       <c r="J57" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K57" t="b">
         <v>0</v>
@@ -7584,10 +7407,10 @@
         <v>1</v>
       </c>
       <c r="O57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P57" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q57" t="b">
         <v>0</v>
@@ -7632,51 +7455,48 @@
         <v>0</v>
       </c>
       <c r="AE57" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF57" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG57">
         <v>0</v>
       </c>
       <c r="AH57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI57" t="s">
         <v>11</v>
       </c>
       <c r="AJ57" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AK57" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL57" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="58" spans="1:39">
+    <row r="58" spans="1:38">
       <c r="A58" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C58" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E58">
         <v>2020</v>
       </c>
       <c r="F58" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G58" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H58">
         <v>185</v>
@@ -7685,7 +7505,7 @@
         <v>32</v>
       </c>
       <c r="J58" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K58" t="b">
         <v>0</v>
@@ -7700,10 +7520,10 @@
         <v>1</v>
       </c>
       <c r="O58" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P58" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q58" t="b">
         <v>1</v>
@@ -7748,51 +7568,48 @@
         <v>0</v>
       </c>
       <c r="AE58" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AF58" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG58">
         <v>0</v>
       </c>
       <c r="AH58" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI58" t="s">
         <v>11</v>
       </c>
       <c r="AJ58" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AK58" t="s">
-        <v>192</v>
-      </c>
-      <c r="AL58" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="59" spans="1:39">
+    <row r="59" spans="1:38">
       <c r="A59" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C59" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E59">
         <v>2003</v>
       </c>
       <c r="F59" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G59" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H59">
         <v>37</v>
@@ -7801,7 +7618,7 @@
         <v>41</v>
       </c>
       <c r="J59" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K59" t="b">
         <v>0</v>
@@ -7816,10 +7633,10 @@
         <v>1</v>
       </c>
       <c r="O59" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P59" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q59" t="b">
         <v>0</v>
@@ -7864,54 +7681,51 @@
         <v>0</v>
       </c>
       <c r="AE59" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AF59" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG59">
         <v>0</v>
       </c>
       <c r="AH59" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI59" t="s">
         <v>12</v>
       </c>
       <c r="AJ59" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK59" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AL59" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM59" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:39">
+    <row r="60" spans="1:38">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C60" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D60" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E60">
         <v>2003</v>
       </c>
       <c r="F60" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G60" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H60">
         <v>52</v>
@@ -7920,7 +7734,7 @@
         <v>49</v>
       </c>
       <c r="J60" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K60" t="b">
         <v>0</v>
@@ -7935,10 +7749,10 @@
         <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P60" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q60" t="b">
         <v>0</v>
@@ -7983,51 +7797,48 @@
         <v>0</v>
       </c>
       <c r="AE60" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AF60" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG60">
         <v>0</v>
       </c>
       <c r="AH60" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI60" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ60" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK60" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL60" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="61" spans="1:39">
+    <row r="61" spans="1:38">
       <c r="A61" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D61" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E61">
         <v>2003</v>
       </c>
       <c r="F61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G61" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H61">
         <v>60</v>
@@ -8036,7 +7847,7 @@
         <v>17</v>
       </c>
       <c r="J61" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K61" t="b">
         <v>0</v>
@@ -8051,10 +7862,10 @@
         <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P61" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q61" t="b">
         <v>0</v>
@@ -8099,51 +7910,48 @@
         <v>0</v>
       </c>
       <c r="AE61" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF61" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG61">
         <v>0</v>
       </c>
       <c r="AH61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI61" t="s">
         <v>11</v>
       </c>
       <c r="AJ61" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK61" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL61" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="62" spans="1:39">
+    <row r="62" spans="1:38">
       <c r="A62" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D62" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E62">
         <v>2012</v>
       </c>
       <c r="F62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G62" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H62">
         <v>184</v>
@@ -8152,7 +7960,7 @@
         <v>58</v>
       </c>
       <c r="J62" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K62" t="b">
         <v>0</v>
@@ -8167,10 +7975,10 @@
         <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P62" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q62" t="b">
         <v>1</v>
@@ -8215,51 +8023,48 @@
         <v>0</v>
       </c>
       <c r="AE62" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AF62" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG62">
         <v>0</v>
       </c>
       <c r="AH62" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI62" t="s">
         <v>11</v>
       </c>
       <c r="AJ62" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AK62" t="s">
-        <v>192</v>
-      </c>
-      <c r="AL62" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="63" spans="1:39">
+    <row r="63" spans="1:38">
       <c r="A63" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C63" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D63" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E63">
         <v>2012</v>
       </c>
       <c r="F63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H63">
         <v>228</v>
@@ -8268,7 +8073,7 @@
         <v>51</v>
       </c>
       <c r="J63" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K63" t="b">
         <v>0</v>
@@ -8283,10 +8088,10 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P63" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q63" t="b">
         <v>0</v>
@@ -8331,51 +8136,48 @@
         <v>0</v>
       </c>
       <c r="AE63" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF63" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG63">
         <v>0</v>
       </c>
       <c r="AH63" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI63" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ63" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK63" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL63" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="64" spans="1:39">
+    <row r="64" spans="1:38">
       <c r="A64" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E64">
         <v>2019</v>
       </c>
       <c r="F64" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G64" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H64">
         <v>37</v>
@@ -8384,7 +8186,7 @@
         <v>43</v>
       </c>
       <c r="J64" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K64" t="b">
         <v>0</v>
@@ -8399,10 +8201,10 @@
         <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P64" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q64" t="b">
         <v>0</v>
@@ -8447,51 +8249,48 @@
         <v>0</v>
       </c>
       <c r="AE64" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF64" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG64">
         <v>0</v>
       </c>
       <c r="AH64" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI64" t="s">
         <v>11</v>
       </c>
       <c r="AJ64" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK64" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL64" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="65" spans="1:39">
+    <row r="65" spans="1:38">
       <c r="A65" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B65" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C65" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E65">
         <v>2019</v>
       </c>
       <c r="F65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G65" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H65">
         <v>252</v>
@@ -8500,7 +8299,7 @@
         <v>45</v>
       </c>
       <c r="J65" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K65" t="b">
         <v>0</v>
@@ -8515,10 +8314,10 @@
         <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P65" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q65" t="b">
         <v>0</v>
@@ -8563,51 +8362,48 @@
         <v>0</v>
       </c>
       <c r="AE65" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF65" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG65">
         <v>0</v>
       </c>
       <c r="AH65" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI65" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ65" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK65" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL65" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="66" spans="1:39">
+    <row r="66" spans="1:38">
       <c r="A66" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B66" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C66" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D66" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E66">
         <v>2019</v>
       </c>
       <c r="F66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G66" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H66">
         <v>259</v>
@@ -8616,7 +8412,7 @@
         <v>42</v>
       </c>
       <c r="J66" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K66" t="b">
         <v>0</v>
@@ -8631,10 +8427,10 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P66" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q66" t="b">
         <v>0</v>
@@ -8679,51 +8475,48 @@
         <v>0</v>
       </c>
       <c r="AE66" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF66" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG66">
         <v>0</v>
       </c>
       <c r="AH66" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI66" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ66" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK66" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL66" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="67" spans="1:39">
+    <row r="67" spans="1:38">
       <c r="A67" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B67" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C67" t="s">
+        <v>85</v>
+      </c>
+      <c r="D67" t="s">
         <v>86</v>
-      </c>
-      <c r="D67" t="s">
-        <v>87</v>
       </c>
       <c r="E67">
         <v>2022</v>
       </c>
       <c r="F67" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G67" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H67">
         <v>133</v>
@@ -8732,7 +8525,7 @@
         <v>26</v>
       </c>
       <c r="J67" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K67" t="b">
         <v>0</v>
@@ -8747,10 +8540,10 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P67" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q67" t="b">
         <v>0</v>
@@ -8795,51 +8588,48 @@
         <v>0</v>
       </c>
       <c r="AE67" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF67" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG67">
         <v>0</v>
       </c>
       <c r="AH67" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI67" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ67" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK67" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL67" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="68" spans="1:39">
+    <row r="68" spans="1:38">
       <c r="A68" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C68" t="s">
+        <v>85</v>
+      </c>
+      <c r="D68" t="s">
         <v>86</v>
-      </c>
-      <c r="D68" t="s">
-        <v>87</v>
       </c>
       <c r="E68">
         <v>2022</v>
       </c>
       <c r="F68" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G68" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H68">
         <v>274</v>
@@ -8848,7 +8638,7 @@
         <v>37</v>
       </c>
       <c r="J68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K68" t="b">
         <v>0</v>
@@ -8863,10 +8653,10 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P68" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q68" t="b">
         <v>0</v>
@@ -8911,51 +8701,48 @@
         <v>0</v>
       </c>
       <c r="AE68" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG68">
         <v>0</v>
       </c>
       <c r="AH68" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI68" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK68" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL68" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="69" spans="1:39">
+    <row r="69" spans="1:38">
       <c r="A69" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C69" t="s">
+        <v>85</v>
+      </c>
+      <c r="D69" t="s">
         <v>86</v>
-      </c>
-      <c r="D69" t="s">
-        <v>87</v>
       </c>
       <c r="E69">
         <v>2022</v>
       </c>
       <c r="F69" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G69" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H69">
         <v>276</v>
@@ -8964,7 +8751,7 @@
         <v>40</v>
       </c>
       <c r="J69" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K69" t="b">
         <v>0</v>
@@ -8979,99 +8766,96 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P69" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q69" t="b">
+        <v>0</v>
+      </c>
+      <c r="R69" t="b">
+        <v>0</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="b">
+        <v>0</v>
+      </c>
+      <c r="U69" t="b">
+        <v>0</v>
+      </c>
+      <c r="V69" t="b">
+        <v>0</v>
+      </c>
+      <c r="W69" t="b">
+        <v>0</v>
+      </c>
+      <c r="X69" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y69" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="s">
         <v>184</v>
       </c>
-      <c r="Q69" t="b">
-        <v>0</v>
-      </c>
-      <c r="R69" t="b">
-        <v>0</v>
-      </c>
-      <c r="S69" t="b">
-        <v>0</v>
-      </c>
-      <c r="T69" t="b">
-        <v>0</v>
-      </c>
-      <c r="U69" t="b">
-        <v>0</v>
-      </c>
-      <c r="V69" t="b">
-        <v>0</v>
-      </c>
-      <c r="W69" t="b">
-        <v>0</v>
-      </c>
-      <c r="X69" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y69" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="s">
-        <v>185</v>
-      </c>
       <c r="AF69" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG69">
         <v>0</v>
       </c>
       <c r="AH69" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI69" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ69" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK69" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL69" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="70" spans="1:39">
+    <row r="70" spans="1:38">
       <c r="A70" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C70" t="s">
+        <v>85</v>
+      </c>
+      <c r="D70" t="s">
         <v>86</v>
-      </c>
-      <c r="D70" t="s">
-        <v>87</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G70" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H70">
         <v>282</v>
@@ -9080,7 +8864,7 @@
         <v>24</v>
       </c>
       <c r="J70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K70" t="b">
         <v>0</v>
@@ -9095,10 +8879,10 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P70" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q70" t="b">
         <v>0</v>
@@ -9143,54 +8927,51 @@
         <v>0</v>
       </c>
       <c r="AE70" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF70" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG70">
         <v>0</v>
       </c>
       <c r="AH70" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI70" t="s">
         <v>11</v>
       </c>
       <c r="AJ70" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK70" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AL70" t="s">
-        <v>197</v>
-      </c>
-      <c r="AM70" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
-    <row r="71" spans="1:39">
+    <row r="71" spans="1:38">
       <c r="A71" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C71" t="s">
+        <v>85</v>
+      </c>
+      <c r="D71" t="s">
         <v>86</v>
-      </c>
-      <c r="D71" t="s">
-        <v>87</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G71" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H71">
         <v>293</v>
@@ -9199,7 +8980,7 @@
         <v>29</v>
       </c>
       <c r="J71" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K71" t="b">
         <v>0</v>
@@ -9214,10 +8995,10 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P71" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q71" t="b">
         <v>0</v>
@@ -9262,51 +9043,48 @@
         <v>0</v>
       </c>
       <c r="AE71" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF71" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG71">
         <v>0</v>
       </c>
       <c r="AH71" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI71" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ71" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK71" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL71" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="72" spans="1:39">
+    <row r="72" spans="1:38">
       <c r="A72" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B72" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C72" t="s">
+        <v>85</v>
+      </c>
+      <c r="D72" t="s">
         <v>86</v>
-      </c>
-      <c r="D72" t="s">
-        <v>87</v>
       </c>
       <c r="E72">
         <v>2022</v>
       </c>
       <c r="F72" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G72" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H72">
         <v>311</v>
@@ -9315,7 +9093,7 @@
         <v>43</v>
       </c>
       <c r="J72" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K72" t="b">
         <v>0</v>
@@ -9330,10 +9108,10 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P72" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q72" t="b">
         <v>0</v>
@@ -9378,28 +9156,25 @@
         <v>0</v>
       </c>
       <c r="AE72" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AF72" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG72">
         <v>0</v>
       </c>
       <c r="AH72" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AI72" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AJ72" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK72" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL72" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
